--- a/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T15:03:25+00:00</t>
+    <t>2023-11-15T15:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T15:06:39+00:00</t>
+    <t>2023-11-17T10:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T10:12:47+00:00</t>
+    <t>2023-11-17T10:19:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-lunar-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T10:19:41+00:00</t>
+    <t>2023-11-20T14:22:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
